--- a/data/trans_orig/IP74A4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP74A4_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
